--- a/data/trans_orig/Q5409A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023 (tasa de respuesta: 96,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>3335</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>73,58%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>378</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13762</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15111</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,82 +2904,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>53,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11727</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>66,14%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>51,5%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>78,96%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>13613</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>10223</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>16841</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>52,25%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>11727</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>9126</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>14129</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>66,14%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>51,47%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>79,69%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>13613</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>10557</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>17076</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>52,25%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,63%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>514</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>497</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>342</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>334</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>353</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>317</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>17058</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28786</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>39263</t>
+          <t>39429</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>494</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>41147</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>69702</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>101977</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>122527</t>
+          <t>122535</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>51090</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Provincia-trans_orig.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>906</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>560</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>423</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>423</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,11%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>466</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>466</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>764</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -4396,22 +4396,22 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>374</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>368</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>286</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>286</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>40496</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>39429</t>
+          <t>46117</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>49991</t>
+          <t>58329</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>49991</t>
+          <t>58329</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>49991</t>
+          <t>58329</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>560</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,17 +6216,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>77759</t>
+          <t>84622</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>75774</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>86273</t>
+          <t>93383</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>112089</t>
+          <t>121580</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>101977</t>
+          <t>110388</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>133015</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -6633,17 +6633,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,17 +6703,17 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>41706</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>56238</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
